--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260814.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260814.xlsx
@@ -611,100 +611,100 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>136,485</t>
+          <t>134,785</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.76%</t>
+          <t>27.55%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>524,888,768</t>
+          <t>15,325</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.22%</t>
+          <t>8.46%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,485</t>
+          <t>97,630</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.19%</t>
+          <t>7.63%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>98,870</t>
+          <t>49,615</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.78%</t>
+          <t>5.72%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>50,215</t>
+          <t>338,018,228</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>5.49%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>119,995</t>
+          <t>118,395</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.20%</t>
+          <t>5.30%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>58,980</t>
+          <t>58,240</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>3.75%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>5,685</t>
+          <t>5,585</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>64,815</t>
+          <t>64,005</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,073</t>
+          <t>17,953</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>44,665</t>
+          <t>44,115</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.84%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>19,525</t>
+          <t>19,285</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>76,245</t>
+          <t>75,295</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>20,095</t>
+          <t>19,845</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>31,260</t>
+          <t>30,870</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>50,575</t>
+          <t>49,945</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -963,254 +963,254 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>11,601</t>
+          <t>11,451</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>35,880</t>
+          <t>3,085,437</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>19,230</t>
+          <t>35,430</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>26,258</t>
+          <t>18,990</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>58,848</t>
+          <t>25,928</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,890</t>
+          <t>58,108</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,436</t>
+          <t>7,790</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>21,108</t>
+          <t>9,336</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>125,755</t>
+          <t>20,848</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>19,517</t>
+          <t>124,185</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,255</t>
+          <t>19,237</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,767,405</t>
+          <t>18,025</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>15,671</t>
+          <t>15,471</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,850</t>
+          <t>42,310</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>37,190</t>
+          <t>36,730</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>11,665</t>
+          <t>11,515</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>83,690,000</t>
+          <t>141,210,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,018,032</t>
+          <t>2,370,817</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
